--- a/Data/thaw_physical_chemical_data.xlsx
+++ b/Data/thaw_physical_chemical_data.xlsx
@@ -1,29 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joyobrien/GitHub/thaw.response/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F3D07E-1B0E-EC40-B8A6-89564BD2C4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1350351-571D-DA4C-AAC5-08D6C6C7DFEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57160" yWindow="8320" windowWidth="27640" windowHeight="16940" activeTab="6" xr2:uid="{4EF39CB8-B893-9843-812C-94FEE9DD1B65}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" activeTab="8" xr2:uid="{4EF39CB8-B893-9843-812C-94FEE9DD1B65}"/>
   </bookViews>
   <sheets>
     <sheet name="Respiration_cum" sheetId="1" r:id="rId1"/>
     <sheet name="pH" sheetId="2" r:id="rId2"/>
     <sheet name="EC" sheetId="4" r:id="rId3"/>
     <sheet name="GWC" sheetId="5" r:id="rId4"/>
-    <sheet name="TC_TN" sheetId="6" r:id="rId5"/>
+    <sheet name="TC_TN_avg" sheetId="6" r:id="rId5"/>
     <sheet name="Resp_TC_TN" sheetId="7" r:id="rId6"/>
     <sheet name="copynumber_all" sheetId="9" r:id="rId7"/>
+    <sheet name="TC_TN_raw" sheetId="10" r:id="rId8"/>
+    <sheet name="TC_TN_raw_edit" sheetId="11" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId8"/>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -73,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="171">
   <si>
     <t>Sample_ID</t>
   </si>
@@ -493,6 +495,99 @@
   </si>
   <si>
     <t>BEO2B_R8_PRE_SOIL</t>
+  </si>
+  <si>
+    <t>Sample ID</t>
+  </si>
+  <si>
+    <t>C  [%]</t>
+  </si>
+  <si>
+    <t>N  [%]</t>
+  </si>
+  <si>
+    <t>ug C</t>
+  </si>
+  <si>
+    <t>ug N</t>
+  </si>
+  <si>
+    <t>AT1-1</t>
+  </si>
+  <si>
+    <t>AT1-2</t>
+  </si>
+  <si>
+    <t>AT1-3</t>
+  </si>
+  <si>
+    <t>AT2-1</t>
+  </si>
+  <si>
+    <t>AT2-2</t>
+  </si>
+  <si>
+    <t>AT2-3</t>
+  </si>
+  <si>
+    <t>AT3-1</t>
+  </si>
+  <si>
+    <t>AT3-2</t>
+  </si>
+  <si>
+    <t>AT3-3</t>
+  </si>
+  <si>
+    <t>AT4-1</t>
+  </si>
+  <si>
+    <t>AT4-2</t>
+  </si>
+  <si>
+    <t>AT4-3</t>
+  </si>
+  <si>
+    <t>FL1-1</t>
+  </si>
+  <si>
+    <t>FL1-2</t>
+  </si>
+  <si>
+    <t>FL1-3</t>
+  </si>
+  <si>
+    <t>FL2-1</t>
+  </si>
+  <si>
+    <t>FL2-2</t>
+  </si>
+  <si>
+    <t>FL2-3</t>
+  </si>
+  <si>
+    <t>UT1-1</t>
+  </si>
+  <si>
+    <t>UT1-2</t>
+  </si>
+  <si>
+    <t>UT1-3</t>
+  </si>
+  <si>
+    <t>UT2-1</t>
+  </si>
+  <si>
+    <t>UT2-2</t>
+  </si>
+  <si>
+    <t>UT2-3</t>
+  </si>
+  <si>
+    <t>FL2C4</t>
+  </si>
+  <si>
+    <t>FL2C5</t>
   </si>
 </sst>
 </file>
@@ -502,7 +597,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -527,6 +622,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3585,4 +3686,1196 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A046B24-C5EA-6743-B787-F406382C0F1F}">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" t="s">
+        <v>143</v>
+      </c>
+      <c r="G1" t="s">
+        <v>144</v>
+      </c>
+      <c r="I1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2">
+        <v>1.6199999999999999E-2</v>
+      </c>
+      <c r="C2">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="D2">
+        <f>B2*100</f>
+        <v>1.6199999999999999</v>
+      </c>
+      <c r="E2">
+        <f>C2*100</f>
+        <v>0.08</v>
+      </c>
+      <c r="F2">
+        <v>311.04000000000002</v>
+      </c>
+      <c r="G2">
+        <v>15.360000000000001</v>
+      </c>
+      <c r="I2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J2">
+        <v>1.6199999999999999</v>
+      </c>
+      <c r="K2">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3">
+        <v>1.47E-2</v>
+      </c>
+      <c r="C3">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:E25" si="0">B3*100</f>
+        <v>1.47</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="F3">
+        <v>285.91499999999996</v>
+      </c>
+      <c r="G3">
+        <v>15.56</v>
+      </c>
+      <c r="I3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J3">
+        <v>1.47</v>
+      </c>
+      <c r="K3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B4">
+        <v>1.49E-2</v>
+      </c>
+      <c r="C4">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>1.49</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>0.09</v>
+      </c>
+      <c r="F4">
+        <v>304.70499999999998</v>
+      </c>
+      <c r="G4">
+        <v>18.404999999999998</v>
+      </c>
+      <c r="I4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J4">
+        <v>1.49</v>
+      </c>
+      <c r="K4">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5">
+        <v>1.3500000000000002E-2</v>
+      </c>
+      <c r="C5">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>1.35</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="F5">
+        <v>286.2</v>
+      </c>
+      <c r="G5">
+        <v>16.96</v>
+      </c>
+      <c r="I5" t="s">
+        <v>148</v>
+      </c>
+      <c r="J5">
+        <v>1.35</v>
+      </c>
+      <c r="K5">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="C6">
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>1.28</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="F6">
+        <v>261.12</v>
+      </c>
+      <c r="G6">
+        <v>16.32</v>
+      </c>
+      <c r="I6" t="s">
+        <v>149</v>
+      </c>
+      <c r="J6">
+        <v>1.28</v>
+      </c>
+      <c r="K6">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7">
+        <v>2.1400000000000002E-2</v>
+      </c>
+      <c r="C7">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>2.14</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>0.13</v>
+      </c>
+      <c r="F7">
+        <v>446.19000000000011</v>
+      </c>
+      <c r="G7">
+        <v>27.105</v>
+      </c>
+      <c r="I7" t="s">
+        <v>150</v>
+      </c>
+      <c r="J7">
+        <v>2.14</v>
+      </c>
+      <c r="K7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="C8">
+        <v>1.8E-3</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>0.18</v>
+      </c>
+      <c r="F8">
+        <v>767.59999999999991</v>
+      </c>
+      <c r="G8">
+        <v>36.36</v>
+      </c>
+      <c r="I8" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8">
+        <v>3.8</v>
+      </c>
+      <c r="K8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9">
+        <v>1.7299999999999999E-2</v>
+      </c>
+      <c r="C9">
+        <v>1E-3</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>1.73</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="F9">
+        <v>389.25</v>
+      </c>
+      <c r="G9">
+        <v>22.5</v>
+      </c>
+      <c r="I9" t="s">
+        <v>152</v>
+      </c>
+      <c r="J9">
+        <v>1.73</v>
+      </c>
+      <c r="K9">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>153</v>
+      </c>
+      <c r="B10">
+        <v>5.2900000000000003E-2</v>
+      </c>
+      <c r="C10">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>5.29</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>0.26</v>
+      </c>
+      <c r="F10">
+        <v>1084.45</v>
+      </c>
+      <c r="G10">
+        <v>53.3</v>
+      </c>
+      <c r="I10" t="s">
+        <v>153</v>
+      </c>
+      <c r="J10">
+        <v>5.29</v>
+      </c>
+      <c r="K10">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B11">
+        <v>1.6799999999999999E-2</v>
+      </c>
+      <c r="C11">
+        <v>8.9999999999999998E-4</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>1.68</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>0.09</v>
+      </c>
+      <c r="F11">
+        <v>372.96</v>
+      </c>
+      <c r="G11">
+        <v>19.979999999999997</v>
+      </c>
+      <c r="I11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J11">
+        <v>1.68</v>
+      </c>
+      <c r="K11">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>155</v>
+      </c>
+      <c r="B12">
+        <v>1.6200000000000003E-2</v>
+      </c>
+      <c r="C12">
+        <v>1E-3</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>1.6200000000000003</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="F12">
+        <v>372.6</v>
+      </c>
+      <c r="G12">
+        <v>23</v>
+      </c>
+      <c r="I12" t="s">
+        <v>155</v>
+      </c>
+      <c r="J12">
+        <v>1.6200000000000003</v>
+      </c>
+      <c r="K12">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13">
+        <v>2.2000000000000002E-2</v>
+      </c>
+      <c r="C13">
+        <v>1.2999999999999999E-3</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>0.13</v>
+      </c>
+      <c r="F13">
+        <v>444.40000000000003</v>
+      </c>
+      <c r="G13">
+        <v>26.259999999999998</v>
+      </c>
+      <c r="I13" t="s">
+        <v>156</v>
+      </c>
+      <c r="J13">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="K13">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B14">
+        <v>0.36469999999999997</v>
+      </c>
+      <c r="C14">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>36.47</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>1.7500000000000002</v>
+      </c>
+      <c r="F14">
+        <v>1276.4499999999998</v>
+      </c>
+      <c r="G14">
+        <v>61.250000000000007</v>
+      </c>
+      <c r="I14" t="s">
+        <v>157</v>
+      </c>
+      <c r="J14">
+        <v>36.47</v>
+      </c>
+      <c r="K14">
+        <v>1.7500000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15">
+        <v>0.39229999999999998</v>
+      </c>
+      <c r="C15">
+        <v>1.9E-2</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>39.229999999999997</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
+        <v>1.9</v>
+      </c>
+      <c r="F15">
+        <v>1154.1466</v>
+      </c>
+      <c r="G15">
+        <v>55.898000000000003</v>
+      </c>
+      <c r="I15" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15">
+        <v>39.229999999999997</v>
+      </c>
+      <c r="K15">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16">
+        <v>0.37969999999999998</v>
+      </c>
+      <c r="C16">
+        <v>2.0499999999999997E-2</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>37.97</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="F16">
+        <v>1142.1375999999998</v>
+      </c>
+      <c r="G16">
+        <v>61.663999999999987</v>
+      </c>
+      <c r="I16" t="s">
+        <v>159</v>
+      </c>
+      <c r="J16">
+        <v>37.97</v>
+      </c>
+      <c r="K16">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>160</v>
+      </c>
+      <c r="B17">
+        <v>0.3987</v>
+      </c>
+      <c r="C17">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>39.869999999999997</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="F17">
+        <v>1330.8606</v>
+      </c>
+      <c r="G17">
+        <v>74.1036</v>
+      </c>
+      <c r="I17" t="s">
+        <v>160</v>
+      </c>
+      <c r="J17">
+        <v>39.869999999999997</v>
+      </c>
+      <c r="K17">
+        <v>2.2200000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18">
+        <v>0.40610000000000002</v>
+      </c>
+      <c r="C18">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>40.61</v>
+      </c>
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>2.19</v>
+      </c>
+      <c r="F18">
+        <v>1421.3500000000001</v>
+      </c>
+      <c r="G18">
+        <v>76.649999999999991</v>
+      </c>
+      <c r="I18" t="s">
+        <v>161</v>
+      </c>
+      <c r="J18">
+        <v>40.61</v>
+      </c>
+      <c r="K18">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B19">
+        <v>0.3836</v>
+      </c>
+      <c r="C19">
+        <v>2.0499999999999997E-2</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>38.36</v>
+      </c>
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="F19">
+        <v>1342.6</v>
+      </c>
+      <c r="G19">
+        <v>71.75</v>
+      </c>
+      <c r="I19" t="s">
+        <v>162</v>
+      </c>
+      <c r="J19">
+        <v>38.36</v>
+      </c>
+      <c r="K19">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20">
+        <v>0.31240000000000001</v>
+      </c>
+      <c r="C20">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>31.240000000000002</v>
+      </c>
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>1.69</v>
+      </c>
+      <c r="F20">
+        <v>920.01800000000003</v>
+      </c>
+      <c r="G20">
+        <v>49.770499999999998</v>
+      </c>
+      <c r="I20" t="s">
+        <v>163</v>
+      </c>
+      <c r="J20">
+        <v>31.240000000000002</v>
+      </c>
+      <c r="K20">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B21">
+        <v>0.21780000000000002</v>
+      </c>
+      <c r="C21">
+        <v>1.1699999999999999E-2</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>21.78</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>1.17</v>
+      </c>
+      <c r="F21">
+        <v>751.41000000000008</v>
+      </c>
+      <c r="G21">
+        <v>40.364999999999995</v>
+      </c>
+      <c r="I21" t="s">
+        <v>164</v>
+      </c>
+      <c r="J21">
+        <v>21.78</v>
+      </c>
+      <c r="K21">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>165</v>
+      </c>
+      <c r="B22">
+        <v>0.39579999999999999</v>
+      </c>
+      <c r="C22">
+        <v>2.1099999999999997E-2</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>39.58</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>2.11</v>
+      </c>
+      <c r="F22">
+        <v>1215.1059999999998</v>
+      </c>
+      <c r="G22">
+        <v>64.776999999999987</v>
+      </c>
+      <c r="I22" t="s">
+        <v>165</v>
+      </c>
+      <c r="J22">
+        <v>39.58</v>
+      </c>
+      <c r="K22">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>166</v>
+      </c>
+      <c r="B23">
+        <v>0.1391</v>
+      </c>
+      <c r="C23">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>13.91</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>0.67</v>
+      </c>
+      <c r="F23">
+        <v>467.37600000000003</v>
+      </c>
+      <c r="G23">
+        <v>22.512</v>
+      </c>
+      <c r="I23" t="s">
+        <v>166</v>
+      </c>
+      <c r="J23">
+        <v>13.91</v>
+      </c>
+      <c r="K23">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>167</v>
+      </c>
+      <c r="B24">
+        <v>0.35289999999999999</v>
+      </c>
+      <c r="C24">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>35.29</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>1.79</v>
+      </c>
+      <c r="F24">
+        <v>1023.41</v>
+      </c>
+      <c r="G24">
+        <v>51.91</v>
+      </c>
+      <c r="I24" t="s">
+        <v>167</v>
+      </c>
+      <c r="J24">
+        <v>35.29</v>
+      </c>
+      <c r="K24">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25">
+        <v>0.1462</v>
+      </c>
+      <c r="C25">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>14.62</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>0.74</v>
+      </c>
+      <c r="F25">
+        <v>526.32000000000005</v>
+      </c>
+      <c r="G25">
+        <v>26.64</v>
+      </c>
+      <c r="I25" t="s">
+        <v>168</v>
+      </c>
+      <c r="J25">
+        <v>14.62</v>
+      </c>
+      <c r="K25">
+        <v>0.74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18E255E2-524B-DE42-A1D5-B60038F57483}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.73</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="3">
+        <v>5.29</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1.68</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1.62</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B8" s="3">
+        <v>36.47</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B9" s="3">
+        <v>39.229999999999997</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="3">
+        <v>37.97</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="D10" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B11" s="3">
+        <v>39.869999999999997</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="D11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B12" s="3">
+        <v>40.61</v>
+      </c>
+      <c r="C12" s="3">
+        <v>2.19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B13" s="3">
+        <v>38.36</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="D13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B14" s="3">
+        <v>31.24</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1.69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="3">
+        <v>21.78</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1.17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B16" s="3">
+        <v>39.58</v>
+      </c>
+      <c r="C16" s="3">
+        <v>2.11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B17" s="3">
+        <v>13.91</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="D17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" s="3">
+        <v>35.29</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1.79</v>
+      </c>
+      <c r="D18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="3">
+        <v>14.62</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.74</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>